--- a/artfynd/A 27518-2026 artfynd.xlsx
+++ b/artfynd/A 27518-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131449357</v>
+        <v>131118226</v>
       </c>
       <c r="B2" t="n">
-        <v>91866</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidmyrbrännan, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731060</v>
+        <v>731023</v>
       </c>
       <c r="R2" t="n">
-        <v>7122797</v>
+        <v>7122947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -739,19 +743,9 @@
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131449360</v>
+        <v>131449355</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -813,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730932</v>
+        <v>731032</v>
       </c>
       <c r="R3" t="n">
-        <v>7122956</v>
+        <v>7122755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,45 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131118226</v>
+        <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>91844</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731023</v>
+        <v>730932</v>
       </c>
       <c r="R4" t="n">
-        <v>7122947</v>
+        <v>7122956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,9 +947,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131118212</v>
+        <v>131449358</v>
       </c>
       <c r="B5" t="n">
-        <v>57914</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,42 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730937</v>
+        <v>731054</v>
       </c>
       <c r="R5" t="n">
-        <v>7122782</v>
+        <v>7122959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,14 +1054,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131118213</v>
+        <v>131118209</v>
       </c>
       <c r="B6" t="n">
-        <v>57914</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730947</v>
+        <v>730914</v>
       </c>
       <c r="R6" t="n">
-        <v>7122781</v>
+        <v>7122796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1200,1216 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131118210</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730928</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7122784</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131118211</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730928</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7122786</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131118212</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730937</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7122782</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131118213</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730947</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7122781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131118214</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730947</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7122761</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131118215</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730951</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7122755</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131118216</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730959</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7122758</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131118217</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>730970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7122745</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131118218</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>730971</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7122743</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131118219</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>730971</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7122736</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131118220</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Lidmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>730978</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7122735</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27518-2026 artfynd.xlsx
+++ b/artfynd/A 27518-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118226</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131449355</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131449360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131449358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118210</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118212</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118213</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118214</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118215</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118216</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118218</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2300,6 +2375,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118219</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,8 +2490,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131118220</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>